--- a/grupos/1AV - Estadisticos 20211.xlsx
+++ b/grupos/1AV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="177">
   <si>
     <t>Materia</t>
   </si>
@@ -203,24 +203,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Bautista Sarao Eutiquio</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Graciela</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Bautista Sarao Eutiquio</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -233,295 +233,295 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>FRIAS</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>EBER</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
   </si>
   <si>
     <t>FIGUEROA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>ROCHA</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>MONFIL</t>
+    <t>CANTU</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>FRIAS</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>TREJO</t>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
+    <t>ITZEEL GUADALUPE</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
   </si>
   <si>
     <t>ORLANDO</t>
   </si>
   <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
   </si>
   <si>
     <t>ARIEL</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>EBER</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CANTU</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ITZEEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
@@ -1052,19 +1052,19 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1094,10 +1094,10 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1114,7 +1114,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1129,19 +1129,19 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1168,7 +1168,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -1191,7 +1191,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -1206,19 +1206,19 @@
         <v>-1</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1245,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1254,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>-1</v>
@@ -1268,7 +1268,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -1283,19 +1283,19 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1322,7 +1322,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1360,19 +1360,19 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1405,7 +1405,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1419,7 +1419,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>9</v>
@@ -1437,19 +1437,19 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1473,10 +1473,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1505,7 +1505,7 @@
         <v>6</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -1514,19 +1514,19 @@
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1559,7 +1559,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1591,19 +1591,19 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1627,7 +1627,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1636,10 +1636,10 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1668,19 +1668,19 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1707,13 +1707,13 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>7</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1730,13 +1730,13 @@
         <v>-1</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>-1</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1754,10 +1754,10 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1784,13 +1784,13 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1813,10 +1813,10 @@
         <v>-1</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -1825,16 +1825,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1867,10 +1867,10 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>-1</v>
@@ -1884,7 +1884,7 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -1899,19 +1899,19 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1938,7 +1938,7 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1961,13 +1961,13 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -1976,19 +1976,19 @@
         <v>-1</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2015,13 +2015,13 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -2053,19 +2053,19 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2130,19 +2130,19 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2207,19 +2207,19 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2252,10 +2252,10 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2266,16 +2266,16 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>9</v>
@@ -2284,19 +2284,19 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2320,19 +2320,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>6</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2343,16 +2343,16 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>6</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -2361,19 +2361,19 @@
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2397,16 +2397,16 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2423,13 +2423,13 @@
         <v>-1</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
         <v>6</v>
@@ -2444,13 +2444,13 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2477,16 +2477,16 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>-1</v>
@@ -2497,16 +2497,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>6</v>
@@ -2515,19 +2515,19 @@
         <v>-1</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2551,19 +2551,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>-1</v>
@@ -2574,16 +2574,16 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>6</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -2592,19 +2592,19 @@
         <v>-1</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2628,19 +2628,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>-1</v>
@@ -2669,19 +2669,19 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2708,13 +2708,13 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2746,19 +2746,19 @@
         <v>-1</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2785,13 +2785,13 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2823,19 +2823,19 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2865,13 +2865,13 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2900,19 +2900,19 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2942,13 +2942,13 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2968,7 +2968,7 @@
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>7</v>
@@ -2977,19 +2977,19 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3022,7 +3022,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3039,16 +3039,16 @@
         <v>-1</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D30">
         <v>-1</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G30">
         <v>-1</v>
@@ -3063,10 +3063,10 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3093,16 +3093,16 @@
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>-1</v>
@@ -3131,19 +3131,19 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3173,10 +3173,10 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3208,19 +3208,19 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3285,19 +3285,19 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3330,10 +3330,10 @@
         <v>7</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3347,13 +3347,13 @@
         <v>-1</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>-1</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -3371,10 +3371,10 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3401,13 +3401,13 @@
         <v>-1</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>5</v>
@@ -3439,19 +3439,19 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3475,13 +3475,13 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>10</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3501,13 +3501,13 @@
         <v>-1</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>-1</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F36">
         <v>5</v>
@@ -3525,10 +3525,10 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3555,13 +3555,13 @@
         <v>-1</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>5</v>
@@ -3593,19 +3593,19 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3632,7 +3632,7 @@
         <v>7</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -3652,7 +3652,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>6</v>
@@ -3661,7 +3661,7 @@
         <v>6</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F38">
         <v>6</v>
@@ -3670,19 +3670,19 @@
         <v>-1</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3706,16 +3706,16 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>6</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>6</v>
@@ -3738,7 +3738,7 @@
         <v>6</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F39">
         <v>7</v>
@@ -3747,19 +3747,19 @@
         <v>-1</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3792,7 +3792,7 @@
         <v>6</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -3809,13 +3809,13 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>6</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F40">
         <v>9</v>
@@ -3824,19 +3824,19 @@
         <v>-1</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I40">
         <v>-1</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3863,13 +3863,13 @@
         <v>6</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V40">
         <v>6</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -3901,19 +3901,19 @@
         <v>6</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3940,16 +3940,16 @@
         <v>6</v>
       </c>
       <c r="U41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>6</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y41">
         <v>6</v>
@@ -3978,19 +3978,19 @@
         <v>8</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4014,19 +4014,19 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U42">
         <v>10</v>
       </c>
       <c r="V42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -4046,10 +4046,10 @@
         <v>-1</v>
       </c>
       <c r="E43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G43">
         <v>-1</v>
@@ -4058,16 +4058,16 @@
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J43">
         <v>-1</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4100,10 +4100,10 @@
         <v>-1</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y43">
         <v>-1</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>17</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4203,30 +4203,30 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>57.5</v>
+        <v>72.5</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>42.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -4235,30 +4235,30 @@
         <v>40</v>
       </c>
       <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>75</v>
+      </c>
+      <c r="G4">
         <v>25</v>
       </c>
-      <c r="E4">
+      <c r="H4">
+        <v>7.4</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>62.5</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>6.6</v>
-      </c>
-      <c r="I4">
-        <v>15</v>
-      </c>
-      <c r="J4">
-        <v>37.5</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -4267,30 +4267,30 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>77.5</v>
+      </c>
+      <c r="G5">
+        <v>22.5</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>67.5</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>6.3</v>
-      </c>
-      <c r="I5">
-        <v>13</v>
-      </c>
-      <c r="J5">
-        <v>32.5</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -4299,30 +4299,30 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>70</v>
+        <v>82.5</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>30</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -4331,25 +4331,25 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4359,7 +4359,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4388,59 +4388,59 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920002</v>
+        <v>21330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920003</v>
+        <v>21330051920006</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
@@ -4448,99 +4448,99 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>21330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920005</v>
+        <v>21330051920380</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920006</v>
+        <v>21330051920380</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920006</v>
+        <v>21330051920380</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920007</v>
+        <v>21330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>61</v>
@@ -4548,19 +4548,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920007</v>
+        <v>21330051920355</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
         <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>62</v>
@@ -4568,139 +4568,139 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920380</v>
+        <v>20330051920018</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
         <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920380</v>
+        <v>20330051920018</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
         <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920380</v>
+        <v>20330051920018</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
         <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920380</v>
+        <v>21330051920013</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920380</v>
+        <v>21330051920014</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
         <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920291</v>
+        <v>21330051920014</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920009</v>
+        <v>20330051920019</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>61</v>
@@ -4708,39 +4708,39 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920009</v>
+        <v>21330051920016</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920009</v>
+        <v>21330051920017</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>62</v>
@@ -4748,79 +4748,79 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920355</v>
+        <v>21330051920017</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
         <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920012</v>
+        <v>21330051920379</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
         <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920012</v>
+        <v>21330051920385</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920012</v>
+        <v>21330051920385</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>65</v>
@@ -4828,19 +4828,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920018</v>
+        <v>21330051920385</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
         <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>61</v>
@@ -4848,179 +4848,179 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920018</v>
+        <v>21330051920020</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920018</v>
+        <v>21330051920020</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920018</v>
+        <v>21330051920020</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920018</v>
+        <v>21330051920023</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920013</v>
+        <v>21330051920024</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920013</v>
+        <v>21330051920024</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920013</v>
+        <v>21330051920024</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920013</v>
+        <v>21330051920025</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920014</v>
+        <v>21330051920026</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
         <v>61</v>
@@ -5028,902 +5028,62 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920014</v>
+        <v>21330051920393</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920014</v>
+        <v>21330051920393</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s">
         <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920014</v>
+        <v>21330051920393</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920014</v>
-      </c>
-      <c r="B37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>125</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920019</v>
-      </c>
-      <c r="B38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920019</v>
-      </c>
-      <c r="B39" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920019</v>
-      </c>
-      <c r="B40" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920019</v>
-      </c>
-      <c r="B41" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920016</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920016</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920016</v>
-      </c>
-      <c r="B44" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" t="s">
-        <v>127</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920016</v>
-      </c>
-      <c r="B45" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" t="s">
-        <v>127</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920017</v>
-      </c>
-      <c r="B46" t="s">
-        <v>85</v>
-      </c>
-      <c r="C46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920017</v>
-      </c>
-      <c r="B47" t="s">
-        <v>85</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>128</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920379</v>
-      </c>
-      <c r="B48" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" t="s">
-        <v>90</v>
-      </c>
-      <c r="D48" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920379</v>
-      </c>
-      <c r="B49" t="s">
-        <v>86</v>
-      </c>
-      <c r="C49" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" t="s">
-        <v>129</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920385</v>
-      </c>
-      <c r="B50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" t="s">
-        <v>130</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920385</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" t="s">
-        <v>130</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920385</v>
-      </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920385</v>
-      </c>
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" t="s">
-        <v>130</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920385</v>
-      </c>
-      <c r="B54" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" t="s">
-        <v>107</v>
-      </c>
-      <c r="D54" t="s">
-        <v>130</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920385</v>
-      </c>
-      <c r="B55" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" t="s">
-        <v>107</v>
-      </c>
-      <c r="D55" t="s">
-        <v>130</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920020</v>
-      </c>
-      <c r="B56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" t="s">
-        <v>131</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920020</v>
-      </c>
-      <c r="B57" t="s">
-        <v>88</v>
-      </c>
-      <c r="C57" t="s">
-        <v>108</v>
-      </c>
-      <c r="D57" t="s">
-        <v>131</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920020</v>
-      </c>
-      <c r="B58" t="s">
-        <v>88</v>
-      </c>
-      <c r="C58" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" t="s">
-        <v>131</v>
-      </c>
-      <c r="E58" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920020</v>
-      </c>
-      <c r="B59" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" t="s">
-        <v>108</v>
-      </c>
-      <c r="D59" t="s">
-        <v>131</v>
-      </c>
-      <c r="E59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920020</v>
-      </c>
-      <c r="B60" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" t="s">
-        <v>108</v>
-      </c>
-      <c r="D60" t="s">
-        <v>131</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920023</v>
-      </c>
-      <c r="B61" t="s">
-        <v>89</v>
-      </c>
-      <c r="C61" t="s">
-        <v>109</v>
-      </c>
-      <c r="D61" t="s">
-        <v>132</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920023</v>
-      </c>
-      <c r="B62" t="s">
-        <v>89</v>
-      </c>
-      <c r="C62" t="s">
-        <v>109</v>
-      </c>
-      <c r="D62" t="s">
-        <v>132</v>
-      </c>
-      <c r="E62" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920023</v>
-      </c>
-      <c r="B63" t="s">
-        <v>89</v>
-      </c>
-      <c r="C63" t="s">
-        <v>109</v>
-      </c>
-      <c r="D63" t="s">
-        <v>132</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920024</v>
-      </c>
-      <c r="B64" t="s">
-        <v>90</v>
-      </c>
-      <c r="C64" t="s">
-        <v>110</v>
-      </c>
-      <c r="D64" t="s">
-        <v>133</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920024</v>
-      </c>
-      <c r="B65" t="s">
-        <v>90</v>
-      </c>
-      <c r="C65" t="s">
-        <v>110</v>
-      </c>
-      <c r="D65" t="s">
-        <v>133</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920024</v>
-      </c>
-      <c r="B66" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66" t="s">
-        <v>110</v>
-      </c>
-      <c r="D66" t="s">
-        <v>133</v>
-      </c>
-      <c r="E66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920024</v>
-      </c>
-      <c r="B67" t="s">
-        <v>90</v>
-      </c>
-      <c r="C67" t="s">
-        <v>110</v>
-      </c>
-      <c r="D67" t="s">
-        <v>133</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920024</v>
-      </c>
-      <c r="B68" t="s">
-        <v>90</v>
-      </c>
-      <c r="C68" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" t="s">
-        <v>133</v>
-      </c>
-      <c r="E68" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920025</v>
-      </c>
-      <c r="B69" t="s">
-        <v>91</v>
-      </c>
-      <c r="C69" t="s">
-        <v>111</v>
-      </c>
-      <c r="D69" t="s">
-        <v>134</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920025</v>
-      </c>
-      <c r="B70" t="s">
-        <v>91</v>
-      </c>
-      <c r="C70" t="s">
-        <v>111</v>
-      </c>
-      <c r="D70" t="s">
-        <v>134</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920026</v>
-      </c>
-      <c r="B71" t="s">
-        <v>92</v>
-      </c>
-      <c r="C71" t="s">
-        <v>109</v>
-      </c>
-      <c r="D71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920026</v>
-      </c>
-      <c r="B72" t="s">
-        <v>92</v>
-      </c>
-      <c r="C72" t="s">
-        <v>109</v>
-      </c>
-      <c r="D72" t="s">
-        <v>135</v>
-      </c>
-      <c r="E72" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920026</v>
-      </c>
-      <c r="B73" t="s">
-        <v>92</v>
-      </c>
-      <c r="C73" t="s">
-        <v>109</v>
-      </c>
-      <c r="D73" t="s">
-        <v>135</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920393</v>
-      </c>
-      <c r="B74" t="s">
-        <v>93</v>
-      </c>
-      <c r="C74" t="s">
-        <v>112</v>
-      </c>
-      <c r="D74" t="s">
-        <v>136</v>
-      </c>
-      <c r="E74" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920393</v>
-      </c>
-      <c r="B75" t="s">
-        <v>93</v>
-      </c>
-      <c r="C75" t="s">
-        <v>112</v>
-      </c>
-      <c r="D75" t="s">
-        <v>136</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920393</v>
-      </c>
-      <c r="B76" t="s">
-        <v>93</v>
-      </c>
-      <c r="C76" t="s">
-        <v>112</v>
-      </c>
-      <c r="D76" t="s">
-        <v>136</v>
-      </c>
-      <c r="E76" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920393</v>
-      </c>
-      <c r="B77" t="s">
-        <v>93</v>
-      </c>
-      <c r="C77" t="s">
-        <v>112</v>
-      </c>
-      <c r="D77" t="s">
-        <v>136</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920393</v>
-      </c>
-      <c r="B78" t="s">
-        <v>93</v>
-      </c>
-      <c r="C78" t="s">
-        <v>112</v>
-      </c>
-      <c r="D78" t="s">
-        <v>136</v>
-      </c>
-      <c r="E78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -5959,126 +5119,126 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920385</v>
+        <v>21330051920380</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920380</v>
+        <v>20330051920018</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920018</v>
+        <v>21330051920385</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
         <v>123</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920014</v>
+        <v>21330051920020</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920020</v>
+        <v>21330051920024</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920024</v>
+        <v>21330051920393</v>
       </c>
       <c r="B7" t="s">
         <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920393</v>
+        <v>21330051920014</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920013</v>
+        <v>21330051920017</v>
       </c>
       <c r="B9" t="s">
         <v>82</v>
@@ -6087,293 +5247,293 @@
         <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920019</v>
+        <v>21330051920003</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920016</v>
+        <v>21330051920005</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920009</v>
+        <v>21330051920006</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920012</v>
+        <v>21330051920007</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920023</v>
+        <v>21330051920009</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920026</v>
+        <v>21330051920355</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920003</v>
+        <v>21330051920013</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920005</v>
+        <v>20330051920019</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920006</v>
+        <v>21330051920016</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920007</v>
+        <v>21330051920379</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920017</v>
+        <v>21330051920023</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920379</v>
+        <v>21330051920025</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920025</v>
+        <v>21330051920026</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920002</v>
+        <v>21330051920001</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920291</v>
+        <v>21330051920002</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920355</v>
+        <v>21330051920004</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920001</v>
+        <v>21330051920008</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -6384,13 +5544,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920004</v>
+        <v>20330051920049</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D27" t="s">
         <v>163</v>
@@ -6401,13 +5561,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920008</v>
+        <v>20330051920291</v>
       </c>
       <c r="B28" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D28" t="s">
         <v>164</v>
@@ -6418,13 +5578,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920049</v>
+        <v>21330051920010</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D29" t="s">
         <v>165</v>
@@ -6435,13 +5595,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920010</v>
+        <v>21330051920011</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D30" t="s">
         <v>166</v>
@@ -6452,13 +5612,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920011</v>
+        <v>21330051920012</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
         <v>167</v>
@@ -6472,10 +5632,10 @@
         <v>20330051920391</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D32" t="s">
         <v>168</v>
@@ -6489,10 +5649,10 @@
         <v>21330051920015</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
         <v>169</v>
@@ -6506,10 +5666,10 @@
         <v>20330051920022</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
         <v>170</v>
@@ -6523,10 +5683,10 @@
         <v>21330051920018</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D35" t="s">
         <v>171</v>
@@ -6540,10 +5700,10 @@
         <v>21330051920356</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
         <v>172</v>
@@ -6557,10 +5717,10 @@
         <v>21330051920019</v>
       </c>
       <c r="B37" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D37" t="s">
         <v>173</v>
@@ -6574,10 +5734,10 @@
         <v>21330051920021</v>
       </c>
       <c r="B38" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D38" t="s">
         <v>174</v>
@@ -6591,10 +5751,10 @@
         <v>21330051920022</v>
       </c>
       <c r="B39" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D39" t="s">
         <v>175</v>
@@ -6608,13 +5768,13 @@
         <v>21330051920027</v>
       </c>
       <c r="B40" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C40" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -6625,10 +5785,10 @@
         <v>21330051920028</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C41" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
@@ -6644,7 +5804,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6679,22 +5839,22 @@
         <v>21330051920003</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -6702,19 +5862,19 @@
         <v>21330051920003</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6722,45 +5882,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920005</v>
+        <v>21330051920009</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>64</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>21330051920009</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6768,45 +5928,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920006</v>
+        <v>21330051920013</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920006</v>
+        <v>21330051920013</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6814,22 +5974,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920007</v>
+        <v>21330051920017</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6837,22 +5997,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920007</v>
+        <v>21330051920017</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6860,36 +6020,36 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920017</v>
+        <v>21330051920026</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
         <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>63</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920017</v>
+        <v>21330051920026</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
         <v>128</v>
@@ -6898,7 +6058,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6906,45 +6066,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920379</v>
+        <v>21330051920002</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>63</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920379</v>
+        <v>21330051920005</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -6952,22 +6112,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920025</v>
+        <v>21330051920006</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
         <v>111</v>
       </c>
-      <c r="D14" t="s">
-        <v>134</v>
-      </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6975,22 +6135,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920025</v>
+        <v>21330051920007</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6998,45 +6158,45 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920002</v>
+        <v>20330051920291</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920291</v>
+        <v>21330051920355</v>
       </c>
       <c r="B17" t="s">
         <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -7044,24 +6204,139 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920355</v>
+        <v>21330051920012</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>63</v>
       </c>
       <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920019</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920016</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920379</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920023</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920025</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20211.xlsx
+++ b/grupos/1AV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="177">
   <si>
     <t>Materia</t>
   </si>
@@ -263,271 +263,271 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>MONFIL</t>
+  </si>
+  <si>
+    <t>FRIAS</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>EDGAR FLORENCIO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>MARIA VALERIA</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>EBER</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSMAR JAHIR</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>MACIEL</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>MONFIL</t>
-  </si>
-  <si>
-    <t>FRIAS</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>CANTU</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>JACOBO</t>
   </si>
   <si>
     <t>ENRIQUEZ</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR FLORENCIO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>MARIA VALERIA</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ITZEEL GUADALUPE</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ORLANDO</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
   </si>
   <si>
     <t>ABRIL</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
     <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>LUIS ARMANDO</t>
-  </si>
-  <si>
-    <t>EBER</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSMAR JAHIR</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>CANTU</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ITZEEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ORLANDO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
   </si>
   <si>
     <t>JOSE EDUARDO</t>
@@ -1298,7 +1298,7 @@
         <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1375,7 +1375,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1606,7 +1606,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1642,7 +1642,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -2068,7 +2068,7 @@
         <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2104,7 +2104,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2222,7 +2222,7 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2258,7 +2258,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2512,7 +2512,7 @@
         <v>6</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H23">
         <v>6</v>
@@ -2566,7 +2566,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2589,7 +2589,7 @@
         <v>5</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -2607,7 +2607,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2643,7 +2643,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2684,7 +2684,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2720,7 +2720,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2743,7 +2743,7 @@
         <v>6</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>6</v>
@@ -2761,7 +2761,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2797,7 +2797,7 @@
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2838,7 +2838,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2874,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2915,7 +2915,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2951,7 +2951,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -3146,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3182,7 +3182,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3300,7 +3300,7 @@
         <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3336,7 +3336,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3454,7 +3454,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3916,7 +3916,7 @@
         <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3952,7 +3952,7 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3993,7 +3993,7 @@
         <v>10</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4171,25 +4171,25 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>57.5</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>42.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4359,7 +4359,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4394,10 +4394,10 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -4417,7 +4417,7 @@
         <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4434,10 +4434,10 @@
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4454,10 +4454,10 @@
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4474,10 +4474,10 @@
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4494,10 +4494,10 @@
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -4514,10 +4514,10 @@
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -4534,10 +4534,10 @@
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4554,10 +4554,10 @@
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -4574,10 +4574,10 @@
         <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -4594,10 +4594,10 @@
         <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -4614,10 +4614,10 @@
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -4634,10 +4634,10 @@
         <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -4654,10 +4654,10 @@
         <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -4674,10 +4674,10 @@
         <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -4688,56 +4688,56 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920019</v>
+        <v>21330051920017</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920016</v>
+        <v>21330051920379</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920017</v>
+        <v>21330051920385</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -4748,56 +4748,56 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920017</v>
+        <v>21330051920385</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920379</v>
+        <v>21330051920385</v>
       </c>
       <c r="B21" t="s">
         <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920385</v>
+        <v>21330051920020</v>
       </c>
       <c r="B22" t="s">
         <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -4808,16 +4808,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920385</v>
+        <v>21330051920020</v>
       </c>
       <c r="B23" t="s">
         <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
@@ -4828,16 +4828,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920385</v>
+        <v>21330051920020</v>
       </c>
       <c r="B24" t="s">
         <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -4848,76 +4848,76 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920020</v>
+        <v>21330051920023</v>
       </c>
       <c r="B25" t="s">
         <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920020</v>
+        <v>21330051920024</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920020</v>
+        <v>21330051920024</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920023</v>
+        <v>21330051920024</v>
       </c>
       <c r="B28" t="s">
         <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -4928,87 +4928,87 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920024</v>
+        <v>21330051920025</v>
       </c>
       <c r="B29" t="s">
         <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920024</v>
+        <v>21330051920026</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920024</v>
+        <v>21330051920393</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920025</v>
+        <v>21330051920393</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920026</v>
+        <v>21330051920393</v>
       </c>
       <c r="B33" t="s">
         <v>89</v>
@@ -5017,72 +5017,12 @@
         <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920393</v>
-      </c>
-      <c r="B34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920393</v>
-      </c>
-      <c r="B35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920393</v>
-      </c>
-      <c r="B36" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" t="s">
-        <v>129</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
         <v>61</v>
       </c>
     </row>
@@ -5125,10 +5065,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -5142,10 +5082,10 @@
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5156,13 +5096,13 @@
         <v>21330051920385</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -5173,13 +5113,13 @@
         <v>21330051920020</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5190,13 +5130,13 @@
         <v>21330051920024</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5207,13 +5147,13 @@
         <v>21330051920393</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -5227,10 +5167,10 @@
         <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -5238,33 +5178,33 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920017</v>
+        <v>21330051920003</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920003</v>
+        <v>21330051920005</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5272,16 +5212,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920005</v>
+        <v>21330051920006</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5289,16 +5229,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920006</v>
+        <v>21330051920007</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
         <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5306,16 +5246,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920007</v>
+        <v>21330051920009</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5323,16 +5263,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920009</v>
+        <v>21330051920355</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
         <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5340,16 +5280,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920355</v>
+        <v>21330051920013</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -5357,16 +5297,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920013</v>
+        <v>21330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -5374,16 +5314,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920019</v>
+        <v>21330051920379</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5391,13 +5331,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920016</v>
+        <v>21330051920023</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
         <v>120</v>
@@ -5408,13 +5348,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920379</v>
+        <v>21330051920025</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
         <v>122</v>
@@ -5425,16 +5365,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920023</v>
+        <v>21330051920026</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -5442,47 +5382,47 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920025</v>
+        <v>21330051920001</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920026</v>
+        <v>21330051920002</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920001</v>
+        <v>21330051920004</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="D23" t="s">
         <v>159</v>
@@ -5493,13 +5433,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920002</v>
+        <v>21330051920008</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
         <v>160</v>
@@ -5510,13 +5450,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920004</v>
+        <v>20330051920049</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
         <v>161</v>
@@ -5527,13 +5467,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920008</v>
+        <v>20330051920291</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -5544,13 +5484,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920049</v>
+        <v>21330051920010</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
         <v>163</v>
@@ -5561,13 +5501,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920291</v>
+        <v>21330051920011</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
         <v>164</v>
@@ -5578,13 +5518,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920010</v>
+        <v>21330051920012</v>
       </c>
       <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
         <v>76</v>
-      </c>
-      <c r="C29" t="s">
-        <v>150</v>
       </c>
       <c r="D29" t="s">
         <v>165</v>
@@ -5595,13 +5535,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920011</v>
+        <v>20330051920019</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
         <v>166</v>
@@ -5612,13 +5552,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920012</v>
+        <v>20330051920391</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
         <v>167</v>
@@ -5629,13 +5569,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920391</v>
+        <v>21330051920015</v>
       </c>
       <c r="B32" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
         <v>168</v>
@@ -5646,13 +5586,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920015</v>
+        <v>21330051920016</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
         <v>169</v>
@@ -5666,10 +5606,10 @@
         <v>20330051920022</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>170</v>
@@ -5683,10 +5623,10 @@
         <v>21330051920018</v>
       </c>
       <c r="B35" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
         <v>171</v>
@@ -5700,10 +5640,10 @@
         <v>21330051920356</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
         <v>172</v>
@@ -5717,10 +5657,10 @@
         <v>21330051920019</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D37" t="s">
         <v>173</v>
@@ -5734,10 +5674,10 @@
         <v>21330051920021</v>
       </c>
       <c r="B38" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D38" t="s">
         <v>174</v>
@@ -5751,10 +5691,10 @@
         <v>21330051920022</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D39" t="s">
         <v>175</v>
@@ -5768,13 +5708,13 @@
         <v>21330051920027</v>
       </c>
       <c r="B40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D40" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -5785,10 +5725,10 @@
         <v>21330051920028</v>
       </c>
       <c r="B41" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
@@ -5804,7 +5744,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5842,10 +5782,10 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5865,10 +5805,10 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5888,10 +5828,10 @@
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5911,10 +5851,10 @@
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5934,10 +5874,10 @@
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5957,10 +5897,10 @@
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5974,39 +5914,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920017</v>
+        <v>21330051920026</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
         <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920017</v>
+        <v>21330051920026</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6020,16 +5960,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920026</v>
+        <v>21330051920002</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6043,22 +5983,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920026</v>
+        <v>21330051920005</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6066,45 +6006,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920002</v>
+        <v>21330051920006</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920005</v>
+        <v>21330051920007</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -6112,45 +6052,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920006</v>
+        <v>20330051920291</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920007</v>
+        <v>21330051920355</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
         <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6158,16 +6098,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920291</v>
+        <v>21330051920012</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6181,16 +6121,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920355</v>
+        <v>21330051920017</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -6204,39 +6144,39 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920012</v>
+        <v>21330051920379</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920019</v>
+        <v>21330051920023</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -6250,16 +6190,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920016</v>
+        <v>21330051920025</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -6268,75 +6208,6 @@
         <v>61</v>
       </c>
       <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920379</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920023</v>
-      </c>
-      <c r="B22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920025</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1AV - Estadisticos 20211.xlsx
+++ b/grupos/1AV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="177">
   <si>
     <t>Materia</t>
   </si>
@@ -203,24 +203,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Saucedo Rivalcoba Graciela</t>
+  </si>
+  <si>
     <t>Bautista Sarao Eutiquio</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Saucedo Rivalcoba Graciela</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -233,6 +233,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
@@ -245,15 +251,30 @@
     <t>COBOS</t>
   </si>
   <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -263,18 +284,42 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>PACHECO</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>ROMAN</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
@@ -287,27 +332,51 @@
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>URBINA</t>
   </si>
   <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>CANTU</t>
   </si>
   <si>
     <t>NOLASCO</t>
   </si>
   <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>MONFIL</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>FRIAS</t>
   </si>
   <si>
+    <t>MORA</t>
+  </si>
+  <si>
     <t>GASPAR</t>
   </si>
   <si>
+    <t>JACOBO</t>
+  </si>
+  <si>
     <t>NAZARIO</t>
   </si>
   <si>
@@ -317,16 +386,37 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>ROSETE</t>
   </si>
   <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>PEÑA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
   </si>
   <si>
     <t>REYES</t>
@@ -335,12 +425,27 @@
     <t>VARGAS</t>
   </si>
   <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>TREJO</t>
   </si>
   <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
     <t>LUIS EDUARDO</t>
   </si>
   <si>
+    <t>ITZEEL GUADALUPE</t>
+  </si>
+  <si>
     <t>KEVIN ISAAC</t>
   </si>
   <si>
@@ -350,15 +455,33 @@
     <t>YOLET</t>
   </si>
   <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
     <t>ERNESTO</t>
   </si>
   <si>
+    <t>ORLANDO</t>
+  </si>
+  <si>
     <t>GERARDO</t>
   </si>
   <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
     <t>MARIA VALERIA</t>
   </si>
   <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
     <t>EDGAR</t>
   </si>
   <si>
@@ -368,18 +491,48 @@
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>VICTOR ISRAEL</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL</t>
+  </si>
+  <si>
     <t>YAIR</t>
   </si>
   <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
     <t>MIGUEL</t>
   </si>
   <si>
     <t>LUIS ARMANDO</t>
   </si>
   <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>GERSON UZIEL</t>
+  </si>
+  <si>
     <t>EBER</t>
   </si>
   <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
     <t>NEMESIO NAHIM</t>
   </si>
   <si>
@@ -392,163 +545,10 @@
     <t>OSVALDO</t>
   </si>
   <si>
+    <t>JAFET</t>
+  </si>
+  <si>
     <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MACIEL</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>CANTU</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ITZEEL GUADALUPE</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ORLANDO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>VICTOR ISRAEL</t>
-  </si>
-  <si>
-    <t>DAVID DANIEL</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>GERSON UZIEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
   </si>
 </sst>
 </file>
@@ -1067,43 +1067,43 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>7</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1132,7 +1132,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1144,37 +1144,37 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1221,43 +1221,43 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1271,7 +1271,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -1289,7 +1289,7 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>7</v>
@@ -1301,22 +1301,22 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1325,16 +1325,16 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1378,25 +1378,25 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1425,7 +1425,7 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -1443,7 +1443,7 @@
         <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>6</v>
@@ -1452,43 +1452,43 @@
         <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>6</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1511,7 +1511,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -1529,25 +1529,25 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1565,7 +1565,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1609,22 +1609,22 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1633,7 +1633,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1683,34 +1683,34 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>6</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1719,7 +1719,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1727,13 +1727,13 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -1742,16 +1742,16 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1760,43 +1760,43 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1804,13 +1804,13 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1819,16 +1819,16 @@
         <v>5</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -1837,43 +1837,43 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>6</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1902,7 +1902,7 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1914,31 +1914,31 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>6</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1950,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1973,7 +1973,7 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>6</v>
@@ -1991,31 +1991,31 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>6</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -2024,10 +2024,10 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2071,31 +2071,31 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2118,7 +2118,7 @@
         <v>9</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>9</v>
@@ -2136,7 +2136,7 @@
         <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>8</v>
@@ -2145,25 +2145,25 @@
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -2172,16 +2172,16 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2225,22 +2225,22 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -2287,7 +2287,7 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -2299,31 +2299,31 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>6</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2332,7 +2332,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2358,7 +2358,7 @@
         <v>5</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -2376,25 +2376,25 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>6</v>
@@ -2403,16 +2403,16 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>6</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2420,7 +2420,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -2435,13 +2435,13 @@
         <v>6</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>6</v>
@@ -2453,31 +2453,31 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -2486,10 +2486,10 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2530,25 +2530,25 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>6</v>
@@ -2566,7 +2566,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2610,31 +2610,31 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2687,22 +2687,22 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2711,7 +2711,7 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2720,7 +2720,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2734,7 +2734,7 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2752,7 +2752,7 @@
         <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>8</v>
@@ -2764,34 +2764,34 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2841,22 +2841,22 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>6</v>
@@ -2865,16 +2865,16 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2918,40 +2918,40 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2965,7 +2965,7 @@
         <v>10</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -2983,7 +2983,7 @@
         <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>6</v>
@@ -2992,34 +2992,34 @@
         <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>6</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -3028,7 +3028,7 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3036,13 +3036,13 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>5</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>6</v>
@@ -3051,16 +3051,16 @@
         <v>5</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>7</v>
@@ -3069,43 +3069,43 @@
         <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>7</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3149,31 +3149,31 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
         <v>6</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3182,7 +3182,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3223,31 +3223,31 @@
         <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>6</v>
@@ -3259,7 +3259,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3303,25 +3303,25 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3336,7 +3336,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3344,13 +3344,13 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3359,16 +3359,16 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>6</v>
@@ -3377,43 +3377,43 @@
         <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>6</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3457,22 +3457,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>8</v>
@@ -3498,13 +3498,13 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>5</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>6</v>
@@ -3513,16 +3513,16 @@
         <v>5</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>6</v>
@@ -3531,43 +3531,43 @@
         <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>6</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3608,34 +3608,34 @@
         <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>7</v>
@@ -3644,7 +3644,7 @@
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3667,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H38">
         <v>6</v>
@@ -3685,43 +3685,43 @@
         <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
         <v>6</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>6</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3744,7 +3744,7 @@
         <v>7</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H39">
         <v>6</v>
@@ -3762,25 +3762,25 @@
         <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T39">
         <v>6</v>
@@ -3789,16 +3789,16 @@
         <v>6</v>
       </c>
       <c r="V39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3821,13 +3821,13 @@
         <v>9</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H40">
         <v>6</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>6</v>
@@ -3839,31 +3839,31 @@
         <v>8</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T40">
         <v>6</v>
       </c>
       <c r="U40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V40">
         <v>6</v>
@@ -3875,7 +3875,7 @@
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3919,34 +3919,34 @@
         <v>7</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
         <v>6</v>
       </c>
       <c r="U41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V41">
         <v>6</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>10</v>
@@ -3996,31 +3996,31 @@
         <v>8</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U42">
         <v>10</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W42">
         <v>10</v>
@@ -4037,13 +4037,13 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>6</v>
       </c>
       <c r="D43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -4052,16 +4052,16 @@
         <v>5</v>
       </c>
       <c r="G43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>6</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K43">
         <v>6</v>
@@ -4070,43 +4070,43 @@
         <v>5</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U43">
         <v>6</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W43">
         <v>6</v>
       </c>
       <c r="X43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -4171,30 +4171,30 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4203,30 +4203,30 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>72.5</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>27.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -4235,19 +4235,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4258,7 +4258,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -4267,19 +4267,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -4299,30 +4299,30 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -4359,7 +4359,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4384,646 +4384,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920003</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920005</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920006</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920007</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920380</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920380</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920380</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920009</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920355</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920018</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920018</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920018</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920013</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920014</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920014</v>
-      </c>
-      <c r="B16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920017</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920379</v>
-      </c>
-      <c r="B18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920385</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920385</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920385</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920020</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" t="s">
-        <v>119</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920020</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920020</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920023</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920024</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>103</v>
-      </c>
-      <c r="D26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920024</v>
-      </c>
-      <c r="B27" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" t="s">
-        <v>121</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920024</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D28" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920025</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920026</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" t="s">
-        <v>123</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920393</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" t="s">
-        <v>105</v>
-      </c>
-      <c r="D31" t="s">
-        <v>124</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920393</v>
-      </c>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920393</v>
-      </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5059,189 +4419,189 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920380</v>
+        <v>21330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920018</v>
+        <v>21330051920002</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920385</v>
+        <v>21330051920003</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920020</v>
+        <v>21330051920004</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920024</v>
+        <v>21330051920005</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920393</v>
+        <v>21330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920014</v>
+        <v>21330051920007</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920003</v>
+        <v>21330051920008</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920005</v>
+        <v>20330051920049</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920006</v>
+        <v>21330051920380</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920007</v>
+        <v>20330051920291</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5249,146 +4609,146 @@
         <v>21330051920009</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920355</v>
+        <v>21330051920010</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920013</v>
+        <v>21330051920355</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920017</v>
+        <v>21330051920011</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920379</v>
+        <v>21330051920012</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920023</v>
+        <v>20330051920018</v>
       </c>
       <c r="B18" t="s">
         <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920025</v>
+        <v>21330051920013</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920026</v>
+        <v>21330051920014</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920001</v>
+        <v>20330051920019</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
         <v>157</v>
@@ -5399,13 +4759,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920002</v>
+        <v>20330051920391</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
         <v>158</v>
@@ -5416,13 +4776,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920004</v>
+        <v>21330051920015</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
         <v>159</v>
@@ -5433,13 +4793,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920008</v>
+        <v>21330051920016</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
         <v>160</v>
@@ -5450,13 +4810,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920049</v>
+        <v>21330051920017</v>
       </c>
       <c r="B25" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
         <v>161</v>
@@ -5467,13 +4827,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920291</v>
+        <v>20330051920022</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -5484,13 +4844,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920010</v>
+        <v>21330051920379</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
         <v>163</v>
@@ -5501,13 +4861,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920011</v>
+        <v>21330051920385</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
         <v>164</v>
@@ -5518,13 +4878,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920012</v>
+        <v>21330051920018</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
         <v>165</v>
@@ -5535,13 +4895,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920019</v>
+        <v>21330051920356</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
         <v>166</v>
@@ -5552,13 +4912,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920391</v>
+        <v>21330051920019</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
         <v>167</v>
@@ -5569,13 +4929,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920015</v>
+        <v>21330051920020</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
         <v>168</v>
@@ -5586,13 +4946,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920016</v>
+        <v>21330051920021</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s">
         <v>169</v>
@@ -5603,13 +4963,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920022</v>
+        <v>21330051920022</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
         <v>170</v>
@@ -5620,13 +4980,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920018</v>
+        <v>21330051920023</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s">
         <v>171</v>
@@ -5637,13 +4997,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920356</v>
+        <v>21330051920024</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="D36" t="s">
         <v>172</v>
@@ -5654,13 +5014,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920019</v>
+        <v>21330051920025</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="C37" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
         <v>173</v>
@@ -5671,13 +5031,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920021</v>
+        <v>21330051920026</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s">
         <v>174</v>
@@ -5688,16 +5048,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920022</v>
+        <v>21330051920027</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="C39" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5705,16 +5065,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920027</v>
+        <v>21330051920028</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -5722,13 +5082,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920028</v>
+        <v>21330051920393</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
@@ -5744,7 +5104,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5776,22 +5136,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920003</v>
+        <v>21330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5799,45 +5159,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920003</v>
+        <v>21330051920006</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>61</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920009</v>
+        <v>21330051920380</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5845,45 +5205,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920009</v>
+        <v>21330051920355</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>61</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920013</v>
+        <v>20330051920018</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5894,42 +5254,42 @@
         <v>21330051920013</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>61</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920026</v>
+        <v>21330051920017</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5937,45 +5297,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920026</v>
+        <v>21330051920379</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>61</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920002</v>
+        <v>21330051920385</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5983,232 +5343,94 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920005</v>
+        <v>21330051920020</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920006</v>
+        <v>21330051920024</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920007</v>
+        <v>21330051920025</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>61</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920291</v>
+        <v>21330051920393</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920355</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920012</v>
-      </c>
-      <c r="B16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920017</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920379</v>
-      </c>
-      <c r="B18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920023</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920025</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>
